--- a/www/download/COUNTRY.FRA.EXI382.xlsx
+++ b/www/download/COUNTRY.FRA.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>França</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920507975460123</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920336196319018</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920336196319018</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.920336196319018</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>24.236</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21.266</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>23.823</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>24.012</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>19.624</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>25.033</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25.672</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>26.041</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>26.161</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26.164</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>26.192</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>26.376</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>26.667</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>27.042</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>27.167</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>26.858</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>26.875</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>27.061</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>27.096</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>25.944</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>26.057</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>26.02</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>25.535</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>24.455</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>25.248</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>25.218</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>24.949</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>21.496</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>18.739</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>21.366</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>21.611</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>17.514</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>22.695</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>23.347</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>23.749</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>23.88</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>23.884</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>23.888</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>24.034</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>24.299</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>24.65</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>24.756</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>24.437</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>24.405</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>24.517</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>24.512</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>23.437</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>23.518</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>23.425</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>22.982</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>21.967</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>22.597</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>22.529</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>22.255</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>36770.617</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>34258.1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>38263.1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>38329.5</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>31156.3</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>39345.1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>39400</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>39732.8</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>38909.7</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>38833.6</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>39640.2</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>39763.3</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>39573.4</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>40570.5</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>40946.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>39994.7</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>40149.8</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>40492.2</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>40346.2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>38672.958</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>38802.193</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>38759.309</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>37956.396</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>36440.482</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>37662.401</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>37775.695</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>37345.852</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>31005.95</t>
+          <t>152929345405.747</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21982.7</t>
+          <t>108131079139.158</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26108.7</t>
+          <t>93818489147.0615</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26337.9</t>
+          <t>103393024093.923</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19995.2</t>
+          <t>102106065772.43</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27841.7</t>
+          <t>113354249272.001</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>27962.4</t>
+          <t>112988209215.502</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28493.6</t>
+          <t>108855676719.363</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28063.1</t>
+          <t>102876991363.395</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28001.6</t>
+          <t>114306989293.95</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>28561.2</t>
+          <t>119766686613.776</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>28649.9</t>
+          <t>122296672413.899</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>34052.5</t>
+          <t>120099809698.357</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>34960.3</t>
+          <t>103337812158.714</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>35343.2</t>
+          <t>99777849958.5263</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>28955.9</t>
+          <t>101902101835.006</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>34548.7</t>
+          <t>104718092039.868</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30437.158</t>
+          <t>103519685898.928</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>28915.8</t>
+          <t>112469287846.215</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>33134.827</t>
+          <t>88952103372.0912</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>33202.866</t>
+          <t>84923370703.1724</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>33068.719</t>
+          <t>89175057941.2603</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>32395.859</t>
+          <t>80174555623.7621</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>30987.237</t>
+          <t>86497277764.4693</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>31878.549</t>
+          <t>84514460331.9083</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>31948.955</t>
+          <t>85416402565.2377</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>31557.836</t>
+          <t>91953312203.9163</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>70266589924.2966</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>38493447695.9485</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>35795994168.2998</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>34289642996.7655</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>38433918692.4781</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>38179179684.9854</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>38563023754.8732</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>36392480261.0316</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>35640424235.042</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>37412867051.9063</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>38414838413.6429</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>35905177803.1894</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>37304980222.0248</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>39139841340.4862</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>34103566955.5056</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>35533476157.5927</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>35831740720.1429</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>38515694404.2719</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>36289486565.0208</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>38171462993.5171</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>35009824358.7663</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>40391209902.8944</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>38588264255.6038</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>44018078249.711</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>42376203954.5731</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>50637112097.3146</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>47244828718.7932</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>17508212.5721875</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9580468.03154238</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6265929.93275327</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8675323.26565333</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10858209.2085262</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>9522711.47403703</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9052238.47317852</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6542074.03004283</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5991021.27175345</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6931568.43406383</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7359652.46819755</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>8052610.56807142</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>8366221.57840529</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>943719.864807828</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6503711.87516194</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5715178.79765319</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6071907.63449647</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4954548.30710228</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5789502.38240231</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4244259.45141392</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>3567346.99691467</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4434536.57318848</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3552422.01363676</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3387950.27956539</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3145589.34087729</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3579313.72072321</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3867919.95236192</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>64718.165831873</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>151003.447970812</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>166182.195362499</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>170205.198134786</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>179233.047966616</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>215996.764293401</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>214802.200901048</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>208242.884209473</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>186511.492422967</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>181538.490260595</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>198333.250988376</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>212285.294591879</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>219058.228570167</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>225061.256621762</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>227515.000745894</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>257062.164776215</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>267332.543892645</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>296564.166142332</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>288090.904891051</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>285512.495817665</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>321322.770065991</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>289322.021265662</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>300027.575313117</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>291536.8173633</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>308969.788578373</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>294545.261022385</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>289430.417686913</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>570059.831902909</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>821695.902272237</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>776500.360686816</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>879765.14398571</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>916432.045923399</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1216156.59641475</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1217193.89827994</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1136740.28576482</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>986876.504799614</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1071561.93101325</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1203627.86690733</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1314727.12835931</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1337661.12956891</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1156506.10944679</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1119023.4643766</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1317936.54088404</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1409956.9343896</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1538442.19248553</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1632714.31779435</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1336615.55040812</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1441501.78984728</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1379666.35961293</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1311422.47407593</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1376038.02465213</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1432509.17797941</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1377293.11190565</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1455681.63619476</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.558738371086529</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.428923587888718</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.27062509069465</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.23189926467039</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.479751202056791</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.270762226173169</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.274890885690337</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.21704704390499</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.212604771062125</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.2515516129475</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.256506048718356</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.20206773081512</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.0871862202490501</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.106784830937801</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.0363490729903821</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.185109279159848</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.0358073789987817</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.209746606979208</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.20319071067045</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.131947679861372</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.0516129034582418</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.181289216925108</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.160473788222039</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.296033855408905</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-0.247725229828415</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.369060481056491</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.332036185282975</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3268.83364949302</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2054.1890013315</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1675.37181355009</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1586.67544291188</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2194.46835060318</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1682.27273342087</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1651.73357411539</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1532.37947960043</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1492.48007684437</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1566.44059001371</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1608.12284049103</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1493.93267051618</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1535.24755018876</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1587.82317811353</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1377.58793648032</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1454.08504143686</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1468.21310059977</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1570.97909223264</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1480.47840098788</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1628.69050437171</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1488.64416789149</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1724.25984894999</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1679.07553161125</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2003.81522232041</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1875.32619810655</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2247.64923783358</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2122.92991073945</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>92128444926.7795</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>38421557805.4525</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>37764305785.8357</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>37524343960.7695</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>38392419117.2152</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>37138109942.1339</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>39172902295.1778</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>38030515092.2512</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>37610911838.3364</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>38670095076.93</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>36989769347.7089</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>33892308832.5414</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>32161201529.9573</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>35355485323.929</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>32429572218.2164</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>29270542174.5153</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>31641030416.1089</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>33855054970.4352</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>30536617648.483</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>34237308967.4743</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>32135766816.2462</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>34020028572.4581</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>35129750098.9412</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>40393359124.5264</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>37972612705.8568</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>42263982066.4778</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.508</t>
+          <t>41447519291.9025</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>91768541558.532</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>36127083711.9667</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>35286236843.6885</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>35150115913.5699</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>36257193308.4178</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>35099644263.0914</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>36683234069.2882</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>36433311165.9467</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>37048237013.5904</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>36644459575.8924</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>35445476633.9509</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>32731974694.4397</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>31022051516.2023</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>34367847204.3416</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>30647324364.7361</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>27901651352.3659</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>28582178338.6834</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>30043541305.8064</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>26620182831.218</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>30525526965.1347</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>27675027582.5684</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>29366477063.6135</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>35096767739.7593</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>40486965601.4413</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>37929556494.5187</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>42517598578.9117</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>39983361212.2421</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>359903368.247529</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2294474093.48582</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2478068942.14724</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2374228047.19961</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2135225808.79747</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2038465679.04252</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2489668225.88955</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1597203926.30453</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>562674824.74597</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2025635501.03763</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1544292713.75806</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1160334138.10169</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1139150013.75502</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>987638119.58736</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1782247853.48038</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1368890822.14938</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3058852077.42543</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>3811513664.62872</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>3916434817.26498</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>3711782002.33961</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>4460739233.67788</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>4653551508.84464</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>32982359.1819371</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-93606476.9148563</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>43056211.3380908</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-253616512.433968</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1464158079.66037</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.106</t>
+          <t>1442.41086082246</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.199</t>
+          <t>1173.09888467885</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1221.97416456084</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>1218.72657443005</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.505</t>
+          <t>1141.66952152572</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>1226.77682308942</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.842</t>
+          <t>1197.68706900235</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.934</t>
+          <t>1199.78104341249</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>1175.17169179209</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>1172.39993300933</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.241</t>
+          <t>1195.62960482294</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.459</t>
+          <t>1192.05708579441</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.629</t>
+          <t>1401.39511914119</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.676</t>
+          <t>1418.26774847955</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>1427.66198093411</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.621</t>
+          <t>1184.92040757937</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.778</t>
+          <t>1415.64023765562</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.888</t>
+          <t>1241.47155800157</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>1179.6589425589</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.967</t>
+          <t>1413.78857110761</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>4.068</t>
+          <t>1411.81092017043</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>4.066</t>
+          <t>1411.67013115844</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>4.178</t>
+          <t>1409.62792034266</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4.361</t>
+          <t>1410.61807652984</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>4.484</t>
+          <t>1410.76058467735</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>4.464</t>
+          <t>1418.13072887247</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4.527</t>
+          <t>1418.04036155439</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>1517.19298510502</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>1610.93294460632</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>1606.14112412422</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>1596.26436781649</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1587.66306563337</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>1571.72931730134</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>1534.74602679957</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>1525.77857993178</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1487.31699858602</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>1484.23788411536</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>1513.44685400164</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>1507.55611161603</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1483.98395020106</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1500.27734635094</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1507.21463540343</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1489.11683669698</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1493.94604651111</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1496.33051254571</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1489.00944788923</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1490.63906991071</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1489.13139300052</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1489.61613271187</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1486.4394629428</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1490.10524670197</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1491.72544990495</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1497.99096274117</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.508</t>
+          <t>1496.90577245033</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>322959.08575795</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>336528.460538698</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>383500.148387223</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>410292.74402721</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>429293.947363676</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>501185.740973792</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>513848.950471786</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>510061.943818249</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>485036.4665226</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>504185.623448865</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>543894.176681818</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>585900.340119625</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>596377.265112372</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>618456.750408249</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>519192.410164042</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>585056.11745651</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>635396.57944318</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>699609.134454475</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>712153.513379253</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>729810.418249734</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>791891.639371121</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>795329.46750906</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>835875.163930415</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>881668.781662704</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>910336.782736307</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>939594.129718972</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>977601.811875649</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>30103980222.6779</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>19889485501.3937</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19529784343.9045</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>21680941597.2147</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>21697998003.5443</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>24966257444.9767</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>23802113012.9096</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>23268181810.841</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>21317401730.7735</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>24106820818.689</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>25856939375.5705</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>26151726045.0473</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>25092091158.3698</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>24629216995.8892</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>18613713461.4343</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>21318573848.2822</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>22187954556.1691</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>21901498996.8548</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>25284118116.9746</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>18826374017.1005</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>17926784196.4698</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>19967573948.2602</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>19419829669.9082</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21038892462.1684</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>21036633868.5275</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>23106491877.4047</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>24479357698.6188</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>297347.564469959</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>307052.37724565</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>333009.481401641</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>362131.146128689</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>385474.709469756</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>475552.246795734</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>482238.947728645</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>468925.775454378</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>454688.195033564</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>481655.170977144</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>541922.511307186</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>591535.420582445</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>614489.746234596</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>648520.16176691</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>539155.58992913</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>618721.68144193</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>687770.526769675</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>735019.715607628</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>740796.191525875</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>761975.78906132</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>808173.80334674</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>812999.058261609</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>867863.078951772</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>913807.7196541</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>941407.615475482</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>976451.382713583</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1015928.93971773</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>36770.617</t>
+          <t>107722826301.217</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>34258.1</t>
+          <t>52323329259.9317</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>38263.1</t>
+          <t>47842857437.4789</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>38329.5</t>
+          <t>50131721400.0299</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>31156.3</t>
+          <t>52052045539.5039</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>39345.1</t>
+          <t>58127572274.4013</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>57876986037.3536</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>39732.8</t>
+          <t>54415235786.5958</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>38909.7</t>
+          <t>53772820311.7151</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>38833.6</t>
+          <t>58645059784.5344</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>39640.2</t>
+          <t>62516946537.2951</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>39763.3</t>
+          <t>60882488077.0012</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>39573.4</t>
+          <t>59502544136.8165</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>40570.5</t>
+          <t>64104572654.5715</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>40946.5</t>
+          <t>53981694257.0452</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>39994.7</t>
+          <t>54740147944.9296</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>40149.8</t>
+          <t>59868526266.6407</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>40492.2</t>
+          <t>59617413240.1407</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>40346.2</t>
+          <t>59101856423.6619</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>38672.958</t>
+          <t>56483057870.7047</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>38802.193</t>
+          <t>51636464494.955</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>38759.309</t>
+          <t>55861578033.2168</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>37956.396</t>
+          <t>57630743935.126</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>36440.482</t>
+          <t>64626531189.7902</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>37662.401</t>
+          <t>61845000883.7804</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>37775.695</t>
+          <t>68947150662.9412</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>37345.852</t>
+          <t>69661283527.482</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>31005.95</t>
+          <t>25611.5212879903</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21982.7</t>
+          <t>29476.0832930486</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26108.7</t>
+          <t>50490.6669855822</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26337.9</t>
+          <t>48161.5978985215</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19995.2</t>
+          <t>43819.2378939195</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>27841.7</t>
+          <t>25633.4941780584</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>27962.4</t>
+          <t>31610.002743141</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>28493.6</t>
+          <t>41136.1683638706</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>28063.1</t>
+          <t>30348.2714890358</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>28001.6</t>
+          <t>22530.452471721</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>28561.2</t>
+          <t>1971.66537463272</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>28649.9</t>
+          <t>-5635.08046281981</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>34052.5</t>
+          <t>-18112.4811222241</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>34960.3</t>
+          <t>-30063.4113586617</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>35343.2</t>
+          <t>-19963.1797650882</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>28955.9</t>
+          <t>-33665.5639854201</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>34548.7</t>
+          <t>-52373.9473264946</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>30437.158</t>
+          <t>-35410.5811531529</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>28915.8</t>
+          <t>-28642.6781466221</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>33134.827</t>
+          <t>-32165.3708115859</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>33202.866</t>
+          <t>-16282.1639756186</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>33068.719</t>
+          <t>-17669.5907525484</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>32395.859</t>
+          <t>-31987.9150213578</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>30987.237</t>
+          <t>-32138.937991396</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>31878.549</t>
+          <t>-31070.8327391751</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>31948.955</t>
+          <t>-36857.2529946116</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>31557.836</t>
+          <t>-38327.1278420771</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>73363.653</t>
+          <t>-77618846078.539</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>56045.557</t>
+          <t>-32433843758.538</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>52151.15</t>
+          <t>-28313073093.5744</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>55083.105</t>
+          <t>-28450779802.8152</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>54294.43</t>
+          <t>-30354047535.9596</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>59013.613</t>
+          <t>-33161314829.4246</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>58887.967</t>
+          <t>-34074873024.444</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>57627.063</t>
+          <t>-31147053975.7548</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>55129.322</t>
+          <t>-32455418580.9415</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>59140.539</t>
+          <t>-34538238965.8454</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>62458.635</t>
+          <t>-36660007161.7246</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>60564.343</t>
+          <t>-34730762031.9539</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>58671.026</t>
+          <t>-34410452978.4467</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>63772.226</t>
+          <t>-39475355658.6822</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>53000.009</t>
+          <t>-35367980795.611</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>54080.794</t>
+          <t>-33421574096.6474</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>54884.204</t>
+          <t>-37680571710.4716</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>55308.468</t>
+          <t>-37715914243.2859</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>58649.437</t>
+          <t>-33817738306.6873</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>48166.23</t>
+          <t>-37656683853.6042</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>46207.374</t>
+          <t>-33709680298.4852</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>47471.813</t>
+          <t>-35894004084.9565</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>44629.709</t>
+          <t>-38210914265.2178</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>47665.988</t>
+          <t>-43587638727.6218</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>46738.85</t>
+          <t>-40808367015.2529</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>47106.793</t>
+          <t>-45840658785.5365</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>49595.376</t>
+          <t>-45181925828.8632</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>425084.828322323</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>405229.957662738</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>405393.389752126</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>457523.48152685</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>436382.642229559</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>438580.040622582</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>448155.272405561</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>472532.081736717</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>488804.629038014</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>507342.047055334</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>523750.09255673</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>577558.744754402</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>574092.342107552</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>601019.10310492</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>621152.035295165</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>615892.938462679</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>640677.486881347</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>654943.029794715</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>659810.865092006</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>676000.607300919</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>691319.089711768</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>718038.500735038</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>722026.977794545</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>738802.354961911</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>760562.584585993</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>807149.921711287</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>799534.358866262</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>17361.874</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>19871.3</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>20078.5</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>20003.1</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>19969.6</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>20132.4</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>19939.4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>19941.6</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>19442.9</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>19365.3</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>19735.1</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>19746.9</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>19667.8</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>20110</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>20286.4</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>19875.9</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>19854.9</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>19955.4</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>19845.1</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>19000.929</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>18930.128</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>18700.397</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>18342.356</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>18325.904</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>18228.445</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>18266.988</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>18282.903</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>631703.529051598</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>642779.131712734</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>652938.833860273</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>611637.512414026</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>738186.642430512</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>741518.842811516</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>773858.860104278</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>805624.777568501</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>838599.318091709</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>866562.770545418</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>898566.429190504</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>910765.156446547</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>1001516.22000447</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>1024808.33885928</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>981987.671695375</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>1046626.54861545</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1067952.66301798</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>1108451.4457385</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1118665.26012465</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>1143578.53095271</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1172368.68881578</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1246250.24598914</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1207499.2633138</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1262284.39080028</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>1297006.47639092</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>1377346.10386089</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1390440.89076182</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>70437.301</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>36035.311</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>34451.232</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>32410.901</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>36058.133</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>35722.391</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>36126.455</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>33982.804</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>33553.376</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>35067.023</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>36180.864</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>33661.461</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>35435.735</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>38410.609</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>33108.365</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>34159.04</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>34640.83</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>37345.817</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>34776.472</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>39050.598</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>35551.634</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>41621.736</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>41316.644</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>46775.95</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>45006.014</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>55137.084</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>50504.48</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-55.98</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-39</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-24.22</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-18.74</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-44.55</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-22.06</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-22.6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-16.15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-16.36</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-20.15</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-21.06</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-14.89</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-3.9</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-8.98</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>6.75</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-15.23</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-18.5</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-16.85</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-15.15</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-6.61</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-20.55</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-21.59</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-33.75</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-29.17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-42.06</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-37.51</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>12.302</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>6.825</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>6.615</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6.246</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>7.526</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>6.753</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6.357</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>4.821</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4.749</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>4.916</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>5.356</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4.168</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>3.811</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>4.477</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4.054</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.686</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>3.777</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.352</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>3.569</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2.892</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2.422</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2.814</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2.483</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>2.354</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2.202</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2.508</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2.565</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>396465.914351896</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>425999.79960529</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>429861.143136727</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>508077.688877427</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>432440.863318734</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>507955.427710555</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>529758.625030101</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>536318.500611275</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>546257.353447534</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>574234.661138378</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>597122.021498488</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>652415.093929891</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>640470.179752355</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>671611.028040733</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>646660.268507918</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>657799.65743935</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>683406.800263431</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>673391.867848824</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>687566.754369594</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>688205.447397932</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>703227.567373607</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>641532.861631624</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>751844.512623227</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>755225.310320288</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>776000.468971125</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>704795.947363908</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>720576.571541228</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>31005949928.19</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21982699999.9956</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>26108699999.9985</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>26337900000.0054</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>19995200000.0087</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>27841700000.0133</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>27962399999.9986</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>28493600000.004</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>28063099999.9939</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>28001600000.0089</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>28561200000.0053</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>28649899999.9855</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>34052500000.0009</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>34960300000.01</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>35343200000.0037</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>28955900000.0171</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>34548699999.9907</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>30437158187.5278</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>28915800000.0085</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>33134827014.6083</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>33202865674.0473</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>33068719088.941</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>32395859309.594</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>30987236837.7582</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>31878549090.6707</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>31948955147.3682</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>31557836016.6576</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>36770616983.2729</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>34258099999.9955</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>38263100000.0016</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>38329500000.0053</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>31156299999.9989</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>39345100000.0036</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>39399999999.9995</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>39732800000.0047</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>38909700000.0069</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>38833600000.0106</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>39640200000.0058</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>39763299999.988</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>39573400000.0008</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>40570500000.0104</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>40946500000.0035</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>39994700000.0079</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>40149799999.9911</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>40492200000.0046</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>40346200000.0122</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>38672958101.9843</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>38802192935.533</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>38759309221.1831</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>37956395935.8891</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>36440481782.7108</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>37662401396.7564</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>37775695380.7503</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>37345852399.8449</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>17361873583.4988</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19871299999.9942</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20078500000.0016</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>20003100000.0004</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>19969600000.0005</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>20132399999.9996</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>19939399999.9957</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19941600000.0056</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>19442900000.0032</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>19365300000.0062</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>19735100000.0111</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>19746899999.9943</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>19667800000.0006</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>20110000000.0077</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>20286400000.0075</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>19875899999.997</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>19854899999.9929</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19955400000.0039</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>19845100000.0046</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>19000928901.5394</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>18930127530.7992</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>18700396534.4827</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>18342355725.2621</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18325904239.7595</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>18228445124.0985</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18266987884.925</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>18282902591.5622</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>24235952.4096585</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21265999.9999984</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23822999.9999939</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>24011999.9999973</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>19624000.000006</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>25032999.9999994</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25672000.0000007</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>26041000.0000009</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>26160999.9999987</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>26164000.000011</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>26191999.9999965</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>26376000.0000023</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>26666999.9999927</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>27041999.9999922</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>27166999.9999991</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>26858000.0000002</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>26875000.0000033</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>27061000.0000034</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>27096000.0000038</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>25943877.953166</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>26056930.3138178</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26019662.6298758</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>25535110.4987111</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>24454971.7970351</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>25247542.3001975</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>25217572.2820281</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>24948699.5689197</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>21495921.0099892</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>18738999.9999988</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21365999.9999931</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>21610999.999998</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>17514000.0000063</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>22694999.9999992</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>23347000.0000007</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>23749000.0000006</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>23879999.9999989</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>23884000.000012</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>23887999.9999958</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>24034000.0000023</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>24298999.9999922</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>24649999.9999923</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>24755999.9999992</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>24437000.0000001</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>24405000.0000037</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>24517000.0000027</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>24512000.0000039</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>23436903.9980633</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>23517926.6569486</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>23425245.2885747</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>22981851.3396918</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>21967134.3741657</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>22596710.906806</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>22528920.9921925</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>22254540.0485394</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>36770616983.2729</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>34258099999.9955</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>38263100000.0016</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>38329500000.0053</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>31156299999.9989</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>39345100000.0036</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>39399999999.9995</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>39732800000.0047</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>38909700000.0069</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>38833600000.0106</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>39640200000.0058</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>39763299999.988</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>39573400000.0008</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>40570500000.0104</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>40946500000.0035</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>39994700000.0079</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>40149799999.9911</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>40492200000.0046</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>40346200000.0122</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>38672958101.9843</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>38802192935.533</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>38759309221.1831</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>37956395935.8891</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>36440481782.7108</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>37662401396.7564</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>37775695380.7503</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>37345852399.8449</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>31005949928.19</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21982699999.9956</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>26108699999.9985</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>26337900000.0054</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>19995200000.0087</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>27841700000.0133</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>27962399999.9986</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>28493600000.004</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>28063099999.9939</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>28001600000.0089</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>28561200000.0053</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>28649899999.9855</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>34052500000.0009</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>34960300000.01</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>35343200000.0037</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>28955900000.0171</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>34548699999.9907</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>30437158187.5278</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>28915800000.0085</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>33134827014.6083</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>33202865674.0473</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>33068719088.941</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>32395859309.594</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>30987236837.7582</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>31878549090.6707</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>31948955147.3682</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>31557836016.6576</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1942369.98729448</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2028936.87741258</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2057549.98603441</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2190284.04861109</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2310533.01769814</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2503705.99087466</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2621936.43407908</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2707518.70878533</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2737255.1959641</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2882816.92400237</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2990534.64041487</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3191111.84973196</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>3348644.92372462</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3392017.29957864</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>3196444.75686196</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3340894.0440918</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3485457.34983882</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3587051.80146028</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3566631.58253858</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3659190.62056528</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>3752808.49205367</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>3750314.86070432</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>3854141.09976864</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>4023259.46447172</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>4136763.69444211</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>4117289.35855292</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>4175986.24796728</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>732428.932133043</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>740962.727009892</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>752171.083712088</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>728825.551824792</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>859391.968858819</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>852925.76050881</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>888162.676510331</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>921766.387280169</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>954686.886287677</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>994971.641724049</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1031448.9238495</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1050719.08305417</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1148139.58009825</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1159077.07870834</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1132599.91792235</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1181279.97621561</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1212979.22090558</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1253597.4742938</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1264928.63713457</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1292264.30575139</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1323985.6109435</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1417836.66103998</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1367241.24470062</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1422330.43152057</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1461576.17939829</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1560883.44551979</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1575349.92803172</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
